--- a/Endowment_Pricing_Engine.xlsx
+++ b/Endowment_Pricing_Engine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="2"/>
+    <workbookView windowWidth="22188" windowHeight="9000" tabRatio="500" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1_Mortality_Table" sheetId="1" r:id="rId1"/>
@@ -327,7 +327,7 @@
     <t>Severe premium surge (+12.8%). Product becomes commercially unviable without redesigning the commission structure.</t>
   </si>
   <si>
-    <t>💡 KEY FINDINGS &amp; ACTUARIAL RECOMMENDATION</t>
+    <t>KEY FINDINGS &amp; ACTUARIAL RECOMMENDATION</t>
   </si>
   <si>
     <t>1. Python DCF Calibration: Excel's commutation rounding errors (Actuarial Drift) were identified and eliminated by calibrating the Base NAP via a Python Discounted Cash Flow model.</t>
@@ -859,7 +859,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -963,6 +963,17 @@
       <right style="thin">
         <color rgb="FFB0B0B0"/>
       </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFB0B0B0"/>
       </top>
@@ -1083,7 +1094,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1095,34 +1106,34 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1207,7 +1218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1311,11 +1322,20 @@
     <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1328,6 +1348,15 @@
     </xf>
     <xf numFmtId="10" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1921,925 +1950,925 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A5" s="55">
+      <c r="A5" s="61">
         <v>25</v>
       </c>
-      <c r="B5" s="56">
+      <c r="B5" s="62">
         <v>0.00175</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="62">
         <f t="shared" ref="C5:C30" si="0">1-B5</f>
         <v>0.99825</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="63">
         <v>100000</v>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="63">
         <f t="shared" ref="E5:E30" si="1">D5*B5</f>
         <v>175</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="62">
         <v>0.00117</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="62">
         <f t="shared" ref="G5:G30" si="2">1-F5</f>
         <v>0.99883</v>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="63">
         <v>100000</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="63">
         <f t="shared" ref="I5:I30" si="3">H5*F5</f>
         <v>117</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A6" s="55">
+      <c r="A6" s="61">
         <v>26</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="62">
         <v>0.00172</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="62">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="63">
         <f t="shared" ref="D6:D30" si="4">D5*C5</f>
         <v>99825</v>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="63">
         <f t="shared" si="1"/>
         <v>171.699</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="62">
         <v>0.0012</v>
       </c>
-      <c r="G6" s="56">
+      <c r="G6" s="62">
         <f t="shared" si="2"/>
         <v>0.9988</v>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="63">
         <f t="shared" ref="H6:H30" si="5">H5*G5</f>
         <v>99883</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="63">
         <f t="shared" si="3"/>
         <v>119.8596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A7" s="55">
+      <c r="A7" s="61">
         <v>27</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="62">
         <v>0.00171</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="62">
         <f t="shared" si="0"/>
         <v>0.99829</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="63">
         <f t="shared" si="4"/>
         <v>99653.301</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="63">
         <f t="shared" si="1"/>
         <v>170.40714471</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="62">
         <v>0.00124</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="62">
         <f t="shared" si="2"/>
         <v>0.99876</v>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="63">
         <f t="shared" si="5"/>
         <v>99763.1404</v>
       </c>
-      <c r="I7" s="57">
+      <c r="I7" s="63">
         <f t="shared" si="3"/>
         <v>123.706294096</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A8" s="55">
+      <c r="A8" s="61">
         <v>28</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="62">
         <v>0.0017</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="62">
         <f t="shared" si="0"/>
         <v>0.9983</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="63">
         <f t="shared" si="4"/>
         <v>99482.89385529</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="63">
         <f t="shared" si="1"/>
         <v>169.120919553993</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="62">
         <v>0.00128</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="62">
         <f t="shared" si="2"/>
         <v>0.99872</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="63">
         <f t="shared" si="5"/>
         <v>99639.434105904</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="63">
         <f t="shared" si="3"/>
         <v>127.538475655557</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A9" s="55">
+      <c r="A9" s="61">
         <v>29</v>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="62">
         <v>0.00172</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="62">
         <f t="shared" si="0"/>
         <v>0.99828</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="63">
         <f t="shared" si="4"/>
         <v>99313.772935736</v>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="63">
         <f t="shared" si="1"/>
         <v>170.819689449466</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="62">
         <v>0.00132</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="62">
         <f t="shared" si="2"/>
         <v>0.99868</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="63">
         <f t="shared" si="5"/>
         <v>99511.8956302484</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="63">
         <f t="shared" si="3"/>
         <v>131.355702231928</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A10" s="55">
+      <c r="A10" s="61">
         <v>30</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="62">
         <v>0.00175</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="62">
         <f t="shared" si="0"/>
         <v>0.99825</v>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="63">
         <f t="shared" si="4"/>
         <v>99142.9532462865</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="63">
         <f t="shared" si="1"/>
         <v>173.500168181001</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="62">
         <v>0.00137</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="62">
         <f t="shared" si="2"/>
         <v>0.99863</v>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="63">
         <f t="shared" si="5"/>
         <v>99380.5399280165</v>
       </c>
-      <c r="I10" s="57">
+      <c r="I10" s="63">
         <f t="shared" si="3"/>
         <v>136.151339701383</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A11" s="55">
+      <c r="A11" s="61">
         <v>31</v>
       </c>
-      <c r="B11" s="56">
+      <c r="B11" s="62">
         <v>0.0018</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="62">
         <f t="shared" si="0"/>
         <v>0.9982</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="63">
         <f t="shared" si="4"/>
         <v>98969.4530781055</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="63">
         <f t="shared" si="1"/>
         <v>178.14501554059</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="62">
         <v>0.00142</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="62">
         <f t="shared" si="2"/>
         <v>0.99858</v>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="63">
         <f t="shared" si="5"/>
         <v>99244.3885883151</v>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="63">
         <f t="shared" si="3"/>
         <v>140.927031795407</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A12" s="55">
+      <c r="A12" s="61">
         <v>32</v>
       </c>
-      <c r="B12" s="56">
+      <c r="B12" s="62">
         <v>0.00187</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="62">
         <f t="shared" si="0"/>
         <v>0.99813</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="63">
         <f t="shared" si="4"/>
         <v>98791.3080625649</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="63">
         <f t="shared" si="1"/>
         <v>184.739746076996</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="62">
         <v>0.00147</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="62">
         <f t="shared" si="2"/>
         <v>0.99853</v>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="63">
         <f t="shared" si="5"/>
         <v>99103.4615565197</v>
       </c>
-      <c r="I12" s="57">
+      <c r="I12" s="63">
         <f t="shared" si="3"/>
         <v>145.682088488084</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A13" s="55">
+      <c r="A13" s="61">
         <v>33</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="62">
         <v>0.00195</v>
       </c>
-      <c r="C13" s="56">
+      <c r="C13" s="62">
         <f t="shared" si="0"/>
         <v>0.99805</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="63">
         <f t="shared" si="4"/>
         <v>98606.5683164879</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="63">
         <f t="shared" si="1"/>
         <v>192.282808217151</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="62">
         <v>0.00154</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="62">
         <f t="shared" si="2"/>
         <v>0.99846</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <f t="shared" si="5"/>
         <v>98957.7794680316</v>
       </c>
-      <c r="I13" s="57">
+      <c r="I13" s="63">
         <f t="shared" si="3"/>
         <v>152.394980380769</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A14" s="55">
+      <c r="A14" s="61">
         <v>34</v>
       </c>
-      <c r="B14" s="56">
+      <c r="B14" s="62">
         <v>0.00205</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="62">
         <f t="shared" si="0"/>
         <v>0.99795</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="63">
         <f t="shared" si="4"/>
         <v>98414.2855082708</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="63">
         <f t="shared" si="1"/>
         <v>201.749285291955</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="62">
         <v>0.00161</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="62">
         <f t="shared" si="2"/>
         <v>0.99839</v>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="63">
         <f t="shared" si="5"/>
         <v>98805.3844876509</v>
       </c>
-      <c r="I14" s="57">
+      <c r="I14" s="63">
         <f t="shared" si="3"/>
         <v>159.076669025118</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A15" s="55">
+      <c r="A15" s="61">
         <v>35</v>
       </c>
-      <c r="B15" s="56">
+      <c r="B15" s="62">
         <v>0.00217</v>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="62">
         <f t="shared" si="0"/>
         <v>0.99783</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="63">
         <f t="shared" si="4"/>
         <v>98212.5362229788</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="63">
         <f t="shared" si="1"/>
         <v>213.121203603864</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="62">
         <v>0.0017</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="62">
         <f t="shared" si="2"/>
         <v>0.9983</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="63">
         <f t="shared" si="5"/>
         <v>98646.3078186258</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="63">
         <f t="shared" si="3"/>
         <v>167.698723291664</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A16" s="55">
+      <c r="A16" s="61">
         <v>36</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="62">
         <v>0.00232</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="62">
         <f t="shared" si="0"/>
         <v>0.99768</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="63">
         <f t="shared" si="4"/>
         <v>97999.415019375</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="63">
         <f t="shared" si="1"/>
         <v>227.35864284495</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="62">
         <v>0.00182</v>
       </c>
-      <c r="G16" s="56">
+      <c r="G16" s="62">
         <f t="shared" si="2"/>
         <v>0.99818</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <f t="shared" si="5"/>
         <v>98478.6090953341</v>
       </c>
-      <c r="I16" s="57">
+      <c r="I16" s="63">
         <f t="shared" si="3"/>
         <v>179.231068553508</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A17" s="55">
+      <c r="A17" s="61">
         <v>37</v>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="62">
         <v>0.00249</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="62">
         <f t="shared" si="0"/>
         <v>0.99751</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="63">
         <f t="shared" si="4"/>
         <v>97772.05637653</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="63">
         <f t="shared" si="1"/>
         <v>243.45242037756</v>
       </c>
-      <c r="F17" s="56">
+      <c r="F17" s="62">
         <v>0.00196</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="62">
         <f t="shared" si="2"/>
         <v>0.99804</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="63">
         <f t="shared" si="5"/>
         <v>98299.3780267806</v>
       </c>
-      <c r="I17" s="57">
+      <c r="I17" s="63">
         <f t="shared" si="3"/>
         <v>192.66678093249</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A18" s="55">
+      <c r="A18" s="61">
         <v>38</v>
       </c>
-      <c r="B18" s="56">
+      <c r="B18" s="62">
         <v>0.00268</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="62">
         <f t="shared" si="0"/>
         <v>0.99732</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="63">
         <f t="shared" si="4"/>
         <v>97528.6039561524</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="63">
         <f t="shared" si="1"/>
         <v>261.376658602489</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="62">
         <v>0.00213</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="62">
         <f t="shared" si="2"/>
         <v>0.99787</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="63">
         <f t="shared" si="5"/>
         <v>98106.7112458481</v>
       </c>
-      <c r="I18" s="57">
+      <c r="I18" s="63">
         <f t="shared" si="3"/>
         <v>208.967294953656</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A19" s="55">
+      <c r="A19" s="61">
         <v>39</v>
       </c>
-      <c r="B19" s="56">
+      <c r="B19" s="62">
         <v>0.0029</v>
       </c>
-      <c r="C19" s="56">
+      <c r="C19" s="62">
         <f t="shared" si="0"/>
         <v>0.9971</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="63">
         <f t="shared" si="4"/>
         <v>97267.22729755</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E19" s="63">
         <f t="shared" si="1"/>
         <v>282.074959162895</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="62">
         <v>0.00232</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="62">
         <f t="shared" si="2"/>
         <v>0.99768</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <f t="shared" si="5"/>
         <v>97897.7439508944</v>
       </c>
-      <c r="I19" s="57">
+      <c r="I19" s="63">
         <f t="shared" si="3"/>
         <v>227.122765966075</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A20" s="55">
+      <c r="A20" s="61">
         <v>40</v>
       </c>
-      <c r="B20" s="56">
+      <c r="B20" s="62">
         <v>0.00315</v>
       </c>
-      <c r="C20" s="56">
+      <c r="C20" s="62">
         <f t="shared" si="0"/>
         <v>0.99685</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="63">
         <f t="shared" si="4"/>
         <v>96985.1523383871</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="63">
         <f t="shared" si="1"/>
         <v>305.503229865919</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="62">
         <v>0.00253</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="62">
         <f t="shared" si="2"/>
         <v>0.99747</v>
       </c>
-      <c r="H20" s="57">
+      <c r="H20" s="63">
         <f t="shared" si="5"/>
         <v>97670.6211849284</v>
       </c>
-      <c r="I20" s="57">
+      <c r="I20" s="63">
         <f t="shared" si="3"/>
         <v>247.106671597869</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A21" s="55">
+      <c r="A21" s="61">
         <v>41</v>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="62">
         <v>0.00342</v>
       </c>
-      <c r="C21" s="56">
+      <c r="C21" s="62">
         <f t="shared" si="0"/>
         <v>0.99658</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="63">
         <f t="shared" si="4"/>
         <v>96679.6491085211</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="63">
         <f t="shared" si="1"/>
         <v>330.644399951142</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="62">
         <v>0.00275</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="62">
         <f t="shared" si="2"/>
         <v>0.99725</v>
       </c>
-      <c r="H21" s="57">
+      <c r="H21" s="63">
         <f t="shared" si="5"/>
         <v>97423.5145133305</v>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="63">
         <f t="shared" si="3"/>
         <v>267.914664911659</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A22" s="55">
+      <c r="A22" s="61">
         <v>42</v>
       </c>
-      <c r="B22" s="56">
+      <c r="B22" s="62">
         <v>0.00371</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="62">
         <f t="shared" si="0"/>
         <v>0.99629</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="63">
         <f t="shared" si="4"/>
         <v>96349.00470857</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="63">
         <f t="shared" si="1"/>
         <v>357.454807468795</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="62">
         <v>0.00298</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="62">
         <f t="shared" si="2"/>
         <v>0.99702</v>
       </c>
-      <c r="H22" s="57">
+      <c r="H22" s="63">
         <f t="shared" si="5"/>
         <v>97155.5998484188</v>
       </c>
-      <c r="I22" s="57">
+      <c r="I22" s="63">
         <f t="shared" si="3"/>
         <v>289.523687548288</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A23" s="55">
+      <c r="A23" s="61">
         <v>43</v>
       </c>
-      <c r="B23" s="56">
+      <c r="B23" s="62">
         <v>0.00403</v>
       </c>
-      <c r="C23" s="56">
+      <c r="C23" s="62">
         <f t="shared" si="0"/>
         <v>0.99597</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="63">
         <f t="shared" si="4"/>
         <v>95991.5499011012</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="63">
         <f t="shared" si="1"/>
         <v>386.845946101438</v>
       </c>
-      <c r="F23" s="56">
+      <c r="F23" s="62">
         <v>0.0032</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G23" s="62">
         <f t="shared" si="2"/>
         <v>0.9968</v>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="63">
         <f t="shared" si="5"/>
         <v>96866.0761608706</v>
       </c>
-      <c r="I23" s="57">
+      <c r="I23" s="63">
         <f t="shared" si="3"/>
         <v>309.971443714786</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A24" s="55">
+      <c r="A24" s="61">
         <v>44</v>
       </c>
-      <c r="B24" s="56">
+      <c r="B24" s="62">
         <v>0.00437</v>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="62">
         <f t="shared" si="0"/>
         <v>0.99563</v>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="63">
         <f t="shared" si="4"/>
         <v>95604.7039549998</v>
       </c>
-      <c r="E24" s="57">
+      <c r="E24" s="63">
         <f t="shared" si="1"/>
         <v>417.792556283349</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="62">
         <v>0.00344</v>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="62">
         <f t="shared" si="2"/>
         <v>0.99656</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="63">
         <f t="shared" si="5"/>
         <v>96556.1047171558</v>
       </c>
-      <c r="I24" s="57">
+      <c r="I24" s="63">
         <f t="shared" si="3"/>
         <v>332.153000227016</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A25" s="55">
+      <c r="A25" s="61">
         <v>45</v>
       </c>
-      <c r="B25" s="56">
+      <c r="B25" s="62">
         <v>0.00473</v>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="62">
         <f t="shared" si="0"/>
         <v>0.99527</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="63">
         <f t="shared" si="4"/>
         <v>95186.9113987164</v>
       </c>
-      <c r="E25" s="57">
+      <c r="E25" s="63">
         <f t="shared" si="1"/>
         <v>450.234090915929</v>
       </c>
-      <c r="F25" s="56">
+      <c r="F25" s="62">
         <v>0.00368</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="62">
         <f t="shared" si="2"/>
         <v>0.99632</v>
       </c>
-      <c r="H25" s="57">
+      <c r="H25" s="63">
         <f t="shared" si="5"/>
         <v>96223.9517169288</v>
       </c>
-      <c r="I25" s="57">
+      <c r="I25" s="63">
         <f t="shared" si="3"/>
         <v>354.104142318298</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A26" s="55">
+      <c r="A26" s="61">
         <v>46</v>
       </c>
-      <c r="B26" s="56">
+      <c r="B26" s="62">
         <v>0.00512</v>
       </c>
-      <c r="C26" s="56">
+      <c r="C26" s="62">
         <f t="shared" si="0"/>
         <v>0.99488</v>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="63">
         <f t="shared" si="4"/>
         <v>94736.6773078005</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="63">
         <f t="shared" si="1"/>
         <v>485.051787815939</v>
       </c>
-      <c r="F26" s="56">
+      <c r="F26" s="62">
         <v>0.00392</v>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="62">
         <f t="shared" si="2"/>
         <v>0.99608</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <f t="shared" si="5"/>
         <v>95869.8475746105</v>
       </c>
-      <c r="I26" s="57">
+      <c r="I26" s="63">
         <f t="shared" si="3"/>
         <v>375.809802492473</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A27" s="55">
+      <c r="A27" s="61">
         <v>47</v>
       </c>
-      <c r="B27" s="56">
+      <c r="B27" s="62">
         <v>0.00553</v>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="62">
         <f t="shared" si="0"/>
         <v>0.99447</v>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="63">
         <f t="shared" si="4"/>
         <v>94251.6255199845</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="63">
         <f t="shared" si="1"/>
         <v>521.211489125515</v>
       </c>
-      <c r="F27" s="56">
+      <c r="F27" s="62">
         <v>0.00419</v>
       </c>
-      <c r="G27" s="56">
+      <c r="G27" s="62">
         <f t="shared" si="2"/>
         <v>0.99581</v>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="63">
         <f t="shared" si="5"/>
         <v>95494.037772118</v>
       </c>
-      <c r="I27" s="57">
+      <c r="I27" s="63">
         <f t="shared" si="3"/>
         <v>400.120018265174</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A28" s="55">
+      <c r="A28" s="61">
         <v>48</v>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="62">
         <v>0.00597</v>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="62">
         <f t="shared" si="0"/>
         <v>0.99403</v>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="63">
         <f t="shared" si="4"/>
         <v>93730.414030859</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="63">
         <f t="shared" si="1"/>
         <v>559.570571764228</v>
       </c>
-      <c r="F28" s="56">
+      <c r="F28" s="62">
         <v>0.00448</v>
       </c>
-      <c r="G28" s="56">
+      <c r="G28" s="62">
         <f t="shared" si="2"/>
         <v>0.99552</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="63">
         <f t="shared" si="5"/>
         <v>95093.9177538528</v>
       </c>
-      <c r="I28" s="57">
+      <c r="I28" s="63">
         <f t="shared" si="3"/>
         <v>426.020751537261</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A29" s="55">
+      <c r="A29" s="61">
         <v>49</v>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="62">
         <v>0.00646</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="62">
         <f t="shared" si="0"/>
         <v>0.99354</v>
       </c>
-      <c r="D29" s="57">
+      <c r="D29" s="63">
         <f t="shared" si="4"/>
         <v>93170.8434590948</v>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="63">
         <f t="shared" si="1"/>
         <v>601.883648745752</v>
       </c>
-      <c r="F29" s="56">
+      <c r="F29" s="62">
         <v>0.00479</v>
       </c>
-      <c r="G29" s="56">
+      <c r="G29" s="62">
         <f t="shared" si="2"/>
         <v>0.99521</v>
       </c>
-      <c r="H29" s="57">
+      <c r="H29" s="63">
         <f t="shared" si="5"/>
         <v>94667.8970023155</v>
       </c>
-      <c r="I29" s="57">
+      <c r="I29" s="63">
         <f t="shared" si="3"/>
         <v>453.459226641091</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A30" s="55">
+      <c r="A30" s="61">
         <v>50</v>
       </c>
-      <c r="B30" s="56">
+      <c r="B30" s="62">
         <v>0.007</v>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="62">
         <f t="shared" si="0"/>
         <v>0.993</v>
       </c>
-      <c r="D30" s="57">
+      <c r="D30" s="63">
         <f t="shared" si="4"/>
         <v>92568.959810349</v>
       </c>
-      <c r="E30" s="57">
+      <c r="E30" s="63">
         <f t="shared" si="1"/>
         <v>647.982718672443</v>
       </c>
-      <c r="F30" s="56">
+      <c r="F30" s="62">
         <v>0.00513</v>
       </c>
-      <c r="G30" s="56">
+      <c r="G30" s="62">
         <f t="shared" si="2"/>
         <v>0.99487</v>
       </c>
-      <c r="H30" s="57">
+      <c r="H30" s="63">
         <f t="shared" si="5"/>
         <v>94214.4377756745</v>
       </c>
-      <c r="I30" s="57">
+      <c r="I30" s="63">
         <f t="shared" si="3"/>
         <v>483.32006578921</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="58" t="s">
+      <c r="A32" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2891,92 +2920,92 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A4" s="5" t="s">
+    <row r="4" ht="38" customHeight="1" spans="1:10">
+      <c r="A4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:10">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="48">
+      <c r="B5" s="51">
         <v>30</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:10">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="48">
+      <c r="B6" s="51">
         <v>15</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="50">
+      <c r="B7" s="53">
         <v>800000000</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="52" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:10">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="C8" s="49" t="s">
+      <c r="B8" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:10">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="55">
         <v>0.2</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="52" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:10">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="52">
+      <c r="B10" s="55">
         <v>0.08</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="52">
+      <c r="B11" s="55">
         <v>1</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="52" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="7.5" customHeight="1"/>
+    <row r="12" ht="17" customHeight="1"/>
     <row r="13" ht="19.5" customHeight="1" spans="1:10">
       <c r="A13" s="5" t="s">
         <v>28</v>
@@ -3049,17 +3078,17 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" ref="G15:G29" si="2">1/(1+$B$8)^A15</f>
-        <v>0.970873786407767</v>
+        <v>0.952380952380952</v>
       </c>
       <c r="H15" s="41">
         <f t="shared" ref="H15:H29" si="3">E15*G15</f>
-        <v>0.969174757281553</v>
+        <v>0.950714285714286</v>
       </c>
       <c r="I15" s="41">
         <f t="shared" ref="I15:I29" si="4">F15*G15</f>
-        <v>0.775339805825243</v>
-      </c>
-      <c r="J15" s="53" t="s">
+        <v>0.760571428571428</v>
+      </c>
+      <c r="J15" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3089,17 +3118,17 @@
       </c>
       <c r="G16" s="41">
         <f t="shared" si="2"/>
-        <v>0.942595909133754</v>
+        <v>0.90702947845805</v>
       </c>
       <c r="H16" s="41">
         <f t="shared" si="3"/>
-        <v>0.939252662833443</v>
+        <v>0.903812380952381</v>
       </c>
       <c r="I16" s="41">
         <f t="shared" si="4"/>
-        <v>0.691289959845414</v>
-      </c>
-      <c r="J16" s="53" t="s">
+        <v>0.665205912380952</v>
+      </c>
+      <c r="J16" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3129,17 +3158,17 @@
       </c>
       <c r="G17" s="41">
         <f t="shared" si="2"/>
-        <v>0.91514165935316</v>
+        <v>0.863837598531476</v>
       </c>
       <c r="H17" s="41">
         <f t="shared" si="3"/>
-        <v>0.910190544032956</v>
+        <v>0.859164049333333</v>
       </c>
       <c r="I17" s="41">
         <f t="shared" si="4"/>
-        <v>0.616308221175596</v>
-      </c>
-      <c r="J17" s="53" t="s">
+        <v>0.581757161084587</v>
+      </c>
+      <c r="J17" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3169,17 +3198,17 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="2"/>
-        <v>0.888487047915689</v>
+        <v>0.822702474791882</v>
       </c>
       <c r="H18" s="41">
         <f t="shared" si="3"/>
-        <v>0.881956963565137</v>
+        <v>0.816655885178222</v>
       </c>
       <c r="I18" s="41">
         <f t="shared" si="4"/>
-        <v>0.549415443235688</v>
-      </c>
-      <c r="J18" s="53" t="s">
+        <v>0.508736110334128</v>
+      </c>
+      <c r="J18" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3209,17 +3238,17 @@
       </c>
       <c r="G19" s="41">
         <f t="shared" si="2"/>
-        <v>0.862608784384164</v>
+        <v>0.783526166468459</v>
       </c>
       <c r="H19" s="41">
         <f t="shared" si="3"/>
-        <v>0.854513545427019</v>
+        <v>0.776173086298673</v>
       </c>
       <c r="I19" s="41">
         <f t="shared" si="4"/>
-        <v>0.489733990534845</v>
-      </c>
-      <c r="J19" s="53" t="s">
+        <v>0.444835947812673</v>
+      </c>
+      <c r="J19" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3249,17 +3278,17 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="2"/>
-        <v>0.837484256683654</v>
+        <v>0.746215396636627</v>
       </c>
       <c r="H20" s="41">
         <f t="shared" si="3"/>
-        <v>0.827824515566449</v>
+        <v>0.737608372096576</v>
       </c>
       <c r="I20" s="41">
         <f t="shared" si="4"/>
-        <v>0.43648307412947</v>
-      </c>
-      <c r="J20" s="53" t="s">
+        <v>0.388915239525187</v>
+      </c>
+      <c r="J20" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3289,17 +3318,17 @@
       </c>
       <c r="G21" s="41">
         <f t="shared" si="2"/>
-        <v>0.813091511343354</v>
+        <v>0.710681330130121</v>
       </c>
       <c r="H21" s="41">
         <f t="shared" si="3"/>
-        <v>0.801848507466344</v>
+        <v>0.700854400641249</v>
       </c>
       <c r="I21" s="41">
         <f t="shared" si="4"/>
-        <v>0.388963882257952</v>
-      </c>
-      <c r="J21" s="53" t="s">
+        <v>0.339973256834219</v>
+      </c>
+      <c r="J21" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3329,17 +3358,17 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="2"/>
-        <v>0.789409234313936</v>
+        <v>0.676839362028687</v>
       </c>
       <c r="H22" s="41">
         <f t="shared" si="3"/>
-        <v>0.776555247264809</v>
+        <v>0.665818355413003</v>
       </c>
       <c r="I22" s="41">
         <f t="shared" si="4"/>
-        <v>0.346558964287223</v>
-      </c>
-      <c r="J22" s="53" t="s">
+        <v>0.297139605286405</v>
+      </c>
+      <c r="J22" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3369,17 +3398,17 @@
       </c>
       <c r="G23" s="41">
         <f t="shared" si="2"/>
-        <v>0.766416732343627</v>
+        <v>0.644608916217797</v>
       </c>
       <c r="H23" s="41">
         <f t="shared" si="3"/>
-        <v>0.751916581749649</v>
+        <v>0.632413297352853</v>
       </c>
       <c r="I23" s="41">
         <f t="shared" si="4"/>
-        <v>0.308718224623202</v>
-      </c>
-      <c r="J23" s="53" t="s">
+        <v>0.259653151859713</v>
+      </c>
+      <c r="J23" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3409,17 +3438,17 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="2"/>
-        <v>0.744093914896725</v>
+        <v>0.613913253540759</v>
       </c>
       <c r="H24" s="41">
         <f t="shared" si="3"/>
-        <v>0.727899052099587</v>
+        <v>0.600551713133838</v>
       </c>
       <c r="I24" s="41">
         <f t="shared" si="4"/>
-        <v>0.274948647019467</v>
-      </c>
-      <c r="J24" s="53" t="s">
+        <v>0.22684585247788</v>
+      </c>
+      <c r="J24" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3449,17 +3478,17 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="2"/>
-        <v>0.722421276598762</v>
+        <v>0.584679289086437</v>
       </c>
       <c r="H25" s="41">
         <f t="shared" si="3"/>
-        <v>0.704472009791722</v>
+        <v>0.570152357369015</v>
       </c>
       <c r="I25" s="41">
         <f t="shared" si="4"/>
-        <v>0.244811605901793</v>
-      </c>
-      <c r="J25" s="53" t="s">
+        <v>0.198134080951589</v>
+      </c>
+      <c r="J25" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3489,17 +3518,17 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="2"/>
-        <v>0.701379880192973</v>
+        <v>0.556837418177559</v>
       </c>
       <c r="H26" s="41">
         <f t="shared" si="3"/>
-        <v>0.681614286910907</v>
+        <v>0.54114517743506</v>
       </c>
       <c r="I26" s="41">
         <f t="shared" si="4"/>
-        <v>0.217918837080428</v>
-      </c>
-      <c r="J26" s="53" t="s">
+        <v>0.17300947181253</v>
+      </c>
+      <c r="J26" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3529,17 +3558,17 @@
       </c>
       <c r="G27" s="41">
         <f t="shared" si="2"/>
-        <v>0.680951339993177</v>
+        <v>0.530321350645295</v>
       </c>
       <c r="H27" s="41">
         <f t="shared" si="3"/>
-        <v>0.659306308647056</v>
+        <v>0.513464313168358</v>
       </c>
       <c r="I27" s="41">
         <f t="shared" si="4"/>
-        <v>0.193923815086671</v>
-      </c>
-      <c r="J27" s="53" t="s">
+        <v>0.151026855369845</v>
+      </c>
+      <c r="J27" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3569,17 +3598,17 @@
       </c>
       <c r="G28" s="41">
         <f t="shared" si="2"/>
-        <v>0.661117805818619</v>
+        <v>0.505067952995519</v>
       </c>
       <c r="H28" s="41">
         <f t="shared" si="3"/>
-        <v>0.637523596333212</v>
+        <v>0.487042906653609</v>
       </c>
       <c r="I28" s="41">
         <f t="shared" si="4"/>
-        <v>0.172515454313516</v>
-      </c>
-      <c r="J28" s="53" t="s">
+        <v>0.131795009305988</v>
+      </c>
+      <c r="J28" s="56" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3609,64 +3638,64 @@
       </c>
       <c r="G29" s="41">
         <f t="shared" si="2"/>
-        <v>0.641861947396717</v>
+        <v>0.48101709809097</v>
       </c>
       <c r="H29" s="41">
         <f t="shared" si="3"/>
-        <v>0.616250114774016</v>
+        <v>0.461823361096698</v>
       </c>
       <c r="I29" s="41">
         <f t="shared" si="4"/>
-        <v>0.153418094015449</v>
-      </c>
-      <c r="J29" s="53" t="s">
+        <v>0.114972895148662</v>
+      </c>
+      <c r="J29" s="56" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" ht="7.5" customHeight="1"/>
     <row r="32" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="50" t="s">
         <v>41</v>
       </c>
       <c r="B33" s="42">
         <f>SUM(H15:H29)</f>
-        <v>11.7402986937439</v>
-      </c>
-      <c r="C33" s="49" t="s">
+        <v>10.2173939418372</v>
+      </c>
+      <c r="C33" s="52" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A34" s="47" t="s">
+      <c r="A34" s="50" t="s">
         <v>43</v>
       </c>
       <c r="B34" s="42">
         <f>SUM(I15:I29)</f>
-        <v>5.86034801933196</v>
-      </c>
-      <c r="C34" s="49" t="s">
+        <v>5.24257197875579</v>
+      </c>
+      <c r="C34" s="52" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A35" s="47" t="s">
+      <c r="A35" s="50" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="41">
         <f>E29</f>
         <v>0.960097599294398</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="52" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3676,9 +3705,9 @@
       </c>
       <c r="B36" s="43">
         <f>$B$7*E29*G29</f>
-        <v>493000091.819212</v>
-      </c>
-      <c r="C36" s="49" t="s">
+        <v>369458688.877358</v>
+      </c>
+      <c r="C36" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3689,10 +3718,10 @@
       <c r="B37" s="43">
         <v>36284823</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="60" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3702,21 +3731,21 @@
       </c>
       <c r="B38" s="43">
         <f>B36/B34</f>
-        <v>84124712.4220127</v>
-      </c>
-      <c r="C38" s="49" t="s">
+        <v>70472792.8151483</v>
+      </c>
+      <c r="C38" s="52" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:4">
-      <c r="A39" s="47" t="s">
+      <c r="A39" s="50" t="s">
         <v>51</v>
       </c>
       <c r="B39" s="44">
         <f>B38/300000000</f>
-        <v>0.280415708073376</v>
-      </c>
-      <c r="C39" s="49" t="s">
+        <v>0.234909309383828</v>
+      </c>
+      <c r="C39" s="52" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3724,9 +3753,9 @@
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A32:C32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3842,11 +3871,11 @@
       </c>
       <c r="D7" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E15)*(1+'2_Pricing_Engine'!$B$8)^(-14)</f>
-        <v>508680285.072666</v>
+        <v>388611693.785351</v>
       </c>
       <c r="E7" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H15))/'2_Pricing_Engine'!E15</f>
-        <v>-35227983.4951456</v>
+        <v>-34556974.2857143</v>
       </c>
       <c r="F7" s="43">
         <f>((F6+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B10)/'1_Mortality_Table'!C10</f>
@@ -3871,11 +3900,11 @@
       </c>
       <c r="D8" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E16)*(1+'2_Pricing_Engine'!$B$8)^(-13)</f>
-        <v>524885487.50235</v>
+        <v>408778079.016849</v>
       </c>
       <c r="E8" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H16))/'2_Pricing_Engine'!E16</f>
-        <v>-69493433.9333659</v>
+        <v>-67530693.0875576</v>
       </c>
       <c r="F8" s="43">
         <f>((F7+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B11)/'1_Mortality_Table'!C11</f>
@@ -3900,11 +3929,11 @@
       </c>
       <c r="D9" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E17)*(1+'2_Pricing_Engine'!$B$8)^(-12)</f>
-        <v>541644928.143048</v>
+        <v>430021122.466704</v>
       </c>
       <c r="E9" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H17))/'2_Pricing_Engine'!E17</f>
-        <v>-102829383.251249</v>
+        <v>-99001406.4375959</v>
       </c>
       <c r="F9" s="43">
         <f>((F8+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B12)/'1_Mortality_Table'!C12</f>
@@ -3929,11 +3958,11 @@
       </c>
       <c r="D10" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E18)*(1+'2_Pricing_Engine'!$B$8)^(-11)</f>
-        <v>558984295.363298</v>
+        <v>452404367.105896</v>
       </c>
       <c r="E10" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H18))/'2_Pricing_Engine'!E18</f>
-        <v>-135268887.592689</v>
+        <v>-129046450.048</v>
       </c>
       <c r="F10" s="43">
         <f>((F9+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B13)/'1_Mortality_Table'!C13</f>
@@ -3958,11 +3987,11 @@
       </c>
       <c r="D11" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E19)*(1+'2_Pricing_Engine'!$B$8)^(-10)</f>
-        <v>576936544.139683</v>
+        <v>476000386.253009</v>
       </c>
       <c r="E11" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H19))/'2_Pricing_Engine'!E19</f>
-        <v>-166846365.507131</v>
+        <v>-157741646.968516</v>
       </c>
       <c r="F11" s="43">
         <f>((F10+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B14)/'1_Mortality_Table'!C14</f>
@@ -3987,11 +4016,11 @@
       </c>
       <c r="D12" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E20)*(1+'2_Pricing_Engine'!$B$8)^(-9)</f>
-        <v>595536955.657651</v>
+        <v>500887331.074091</v>
       </c>
       <c r="E12" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H20))/'2_Pricing_Engine'!E20</f>
-        <v>-197597177.510781</v>
+        <v>-185160984.334273</v>
       </c>
       <c r="F12" s="43">
         <f>((F11+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B15)/'1_Mortality_Table'!C15</f>
@@ -4001,7 +4030,7 @@
         <f>F12/'2_Pricing_Engine'!$B$7</f>
         <v>0.313150520020606</v>
       </c>
-      <c r="J12" s="45"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10">
       <c r="A13" s="36">
@@ -4017,11 +4046,11 @@
       </c>
       <c r="D13" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E21)*(1+'2_Pricing_Engine'!$B$8)^(-8)</f>
-        <v>614829468.694752</v>
+        <v>527154696.52373</v>
       </c>
       <c r="E13" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H21))/'2_Pricing_Engine'!E21</f>
-        <v>-227559550.554717</v>
+        <v>-211378503.0191</v>
       </c>
       <c r="F13" s="43">
         <f>((F12+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B16)/'1_Mortality_Table'!C16</f>
@@ -4046,11 +4075,11 @@
       </c>
       <c r="D14" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E22)*(1+'2_Pricing_Engine'!$B$8)^(-7)</f>
-        <v>634855142.059323</v>
+        <v>554894117.702997</v>
       </c>
       <c r="E14" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H22))/'2_Pricing_Engine'!E22</f>
-        <v>-256771162.591105</v>
+        <v>-236465145.781577</v>
       </c>
       <c r="F14" s="43">
         <f>((F13+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B17)/'1_Mortality_Table'!C17</f>
@@ -4075,11 +4104,11 @@
       </c>
       <c r="D15" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E23)*(1+'2_Pricing_Engine'!$B$8)^(-6)</f>
-        <v>655657959.652973</v>
+        <v>584204491.625704</v>
       </c>
       <c r="E15" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H23))/'2_Pricing_Engine'!E23</f>
-        <v>-285270453.973201</v>
+        <v>-260490095.752629</v>
       </c>
       <c r="F15" s="43">
         <f>((F14+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B18)/'1_Mortality_Table'!C18</f>
@@ -4104,11 +4133,11 @@
       </c>
       <c r="D16" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E24)*(1+'2_Pricing_Engine'!$B$8)^(-5)</f>
-        <v>677291844.79246</v>
+        <v>615198792.705836</v>
       </c>
       <c r="E16" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H24))/'2_Pricing_Engine'!E24</f>
-        <v>-313099460.389342</v>
+        <v>-283523447.865668</v>
       </c>
       <c r="F16" s="43">
         <f>((F15+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B19)/'1_Mortality_Table'!C19</f>
@@ -4133,11 +4162,11 @@
       </c>
       <c r="D17" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E25)*(1+'2_Pricing_Engine'!$B$8)^(-4)</f>
-        <v>699815017.441173</v>
+        <v>647999932.127329</v>
       </c>
       <c r="E17" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H25))/'2_Pricing_Engine'!E25</f>
-        <v>-340301768.388906</v>
+        <v>-305634353.3939</v>
       </c>
       <c r="F17" s="43">
         <f>((F16+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B20)/'1_Mortality_Table'!C20</f>
@@ -4162,11 +4191,11 @@
       </c>
       <c r="D18" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E26)*(1+'2_Pricing_Engine'!$B$8)^(-3)</f>
-        <v>723283096.153253</v>
+        <v>682734882.030239</v>
       </c>
       <c r="E18" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H26))/'2_Pricing_Engine'!E26</f>
-        <v>-366919039.210323</v>
+        <v>-326887957.130354</v>
       </c>
       <c r="F18" s="43">
         <f>((F17+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B21)/'1_Mortality_Table'!C21</f>
@@ -4191,11 +4220,11 @@
       </c>
       <c r="D19" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E27)*(1+'2_Pricing_Engine'!$B$8)^(-2)</f>
-        <v>747755762.918277</v>
+        <v>719541123.70068</v>
       </c>
       <c r="E19" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H27))/'2_Pricing_Engine'!E27</f>
-        <v>-392993576.805829</v>
+        <v>-347347843.865755</v>
       </c>
       <c r="F19" s="43">
         <f>((F18+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B22)/'1_Mortality_Table'!C22</f>
@@ -4220,11 +4249,11 @@
       </c>
       <c r="D20" s="42">
         <f>'2_Pricing_Engine'!$B$7*('2_Pricing_Engine'!E29/'2_Pricing_Engine'!E28)*(1+'2_Pricing_Engine'!$B$8)^(-1)</f>
-        <v>773304854.368932</v>
+        <v>758575238.095238</v>
       </c>
       <c r="E20" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H28))/'2_Pricing_Engine'!E28</f>
-        <v>-418572291.881848</v>
+        <v>-367079621.021739</v>
       </c>
       <c r="F20" s="43">
         <f>((F19+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B23)/'1_Mortality_Table'!C23</f>
@@ -4253,7 +4282,7 @@
       </c>
       <c r="E21" s="42">
         <f>'2_Pricing_Engine'!$B$37*('2_Pricing_Engine'!$B$32-SUM('2_Pricing_Engine'!H15:H29))/'2_Pricing_Engine'!E29</f>
-        <v>-443699328.466921</v>
+        <v>-386144420.081144</v>
       </c>
       <c r="F21" s="43">
         <f>((F20+'2_Pricing_Engine'!$B$37)*1.05-800000000*'1_Mortality_Table'!B24)/'1_Mortality_Table'!C24</f>
@@ -4270,7 +4299,7 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="46"/>
+      <c r="A25" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">
